--- a/daily_matches/job_matches_2026-07-24.xlsx
+++ b/daily_matches/job_matches_2026-07-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Analyst IV/ Data Scientist AI/ML Specialist</t>
+          <t>Python + Gen AI Developer - New York</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TELEWORLD SOLUTIONS INC</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, MLflow, Docker, Kubernetes, Git, Snowflake, Databricks, Hadoop, MongoDB, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=968b86a37881afb4</t>
+          <t>https://www.indeed.com/viewjob?jk=11c3a045d64529ec</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Platform Engineer IV</t>
+          <t>Senior AI DevOps Engineer (AI Ops / Platform Engineering) (Hybrid)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Athena, Data Lake, MLflow, FastAPI, Docker, CI/CD</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Azure ML, MLflow, Docker, Kubernetes, AKS, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a6f5499c457885c</t>
+          <t>https://www.indeed.com/viewjob?jk=179f845817d9c394</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Ad Serving</t>
+          <t>Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Best Buy</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Glue, Athena, Kinesis, Dataflow, Apache Airflow, CI/CD, Kafka, Python</t>
+          <t>RAG, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3751536eef408193</t>
+          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>AI Solutions Architect | US</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ACI Worldwide</t>
+          <t>Cuesta Partners</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norcross, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+          <t>LangChain, RAG, Copilot, Hugging Face, TensorFlow, PyTorch, OpenCV, BigQuery, MLflow, Docker</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67fe73c4a60c4cf4</t>
+          <t>https://www.indeed.com/viewjob?jk=96a29f61f02164cc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Omitron Inc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R, Java</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025ebe3ef0840042</t>
+          <t>https://www.indeed.com/viewjob?jk=ec43ad9e8184093c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer I - Systems Engineering</t>
+          <t>Senior Software Developer, Automation</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Temple Terrace, FL, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Docker, CI/CD, Jenkins, Git, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MySQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c562e755de95d9c</t>
+          <t>https://www.indeed.com/viewjob?jk=36278831392884e9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pncpl AI Data Scientist</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Python, R</t>
+          <t>Data Scientist, RAG, Copilot, Data Lake, Git, Snowflake, Kafka, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6999325f7a0ca4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbdf62f4fcd37bb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I-II, Integration Platform Engineering</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, Kafka, R</t>
+          <t>LangChain, RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5777ab28ff195025</t>
+          <t>https://www.indeed.com/viewjob?jk=23122d038602c127</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IT Database Engineer</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kuehne+Nagel</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Naugatuck, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, EC2, CI/CD, Terraform, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>LangChain, RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c73cae1a3da2412</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c550bf8810c96</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - AI/ML Data Science</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, Prompt Engineering, S3, Git, Python, SQL, R, Java</t>
+          <t>LangChain, RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed89b30e8c30a6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=cb19fdabfeceb391</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (FDE) - AI Native Analyst - Dallas ATC - NAELFY26</t>
+          <t>Senior Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, CI/CD, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Gemini, S3, CI/CD, Terraform, Git, Hadoop, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b555e3ab1e2c3b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=894c050699a8cfaa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Engineer - Philadelphia</t>
+          <t>AWS/EKS Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dechert LLP</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Python, SQL, R, Java</t>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6153698e04981af1</t>
+          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineer - New York</t>
+          <t>Senior Software Engineer-Data Operations (Databricks/AI)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dechert LLP</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Data Lake, CI/CD, Git, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfee2c69b0b26a82</t>
+          <t>https://www.indeed.com/viewjob?jk=22eb530ec4c57c3c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Engineer - Boston</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dechert LLP</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ce4800fbf104347</t>
+          <t>https://www.indeed.com/viewjob?jk=f28f64ff4a82786b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer - Washington D.C.</t>
+          <t>AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dechert LLP</t>
+          <t>hr@brxio.com</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ce1fb19e4ef14c</t>
+          <t>https://www.indeed.com/viewjob?jk=c7cf07a83a749259</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Scientist III, Data Sciences</t>
+          <t>Power BI Developer (Hybrid)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Synapse, Git, Snowflake, Databricks, Power BI, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,392 +1021,112 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3acd2727e9cbce</t>
+          <t>https://www.indeed.com/viewjob?jk=d752c9fe0b8d8e6b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Commercial Analytics Engineer Business Decision Intelligence</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>Cirque du Soleil</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Franklin Lakes, NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, BigQuery, Snowflake, Databricks, BigQuery, Tableau, Power BI, SQL, R</t>
+          <t>Git, Snowflake, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1682fc21a41b90bc</t>
+          <t>https://www.indeed.com/viewjob?jk=1bfd1c9155d948dd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AI Driven Test Automation Architect</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Pinecone, CI/CD, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dccf85cb629f63b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a1e8850a1b63516</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, NoSQL, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Pinecone, CI/CD, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4fc216d4e8e348b</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Forward Deployed AI Engineer (GenAI, AWS)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Provectus</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6f6690ffab0886</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer | Cloud</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ExtraHop Networks</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6228473c54a358ed</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Full Stack / IOT Developer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=707d0b3d2b4923f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Forward Deployed Engineers (FDE)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Kubernetes, Git, PostgreSQL, MySQL, MongoDB, NoSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c213700e32ac5f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Sr AI Engineer - AI Platform</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Lowe's Home Improvement</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e88bfedacfe896d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Consultant, Java Developer - Integrated Eligibility</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Lake Mary, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Git, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8f07f5fe67ae419</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Event Technology</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, R, Java, Scala, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4dd9386f168f598</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>GM Financial</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Arlington, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Generative AI, Jenkins, Terraform, Git, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdcb0ba13a35657</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7d163b37ed7c13</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-24.xlsx
+++ b/daily_matches/job_matches_2026-07-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Python + Gen AI Developer - New York</t>
+          <t>AI Engineer (LLM &amp; GenAI)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Flipped.ai</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, PyTorch, GCP Vertex AI, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c3a045d64529ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c681313934b33c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI DevOps Engineer (AI Ops / Platform Engineering) (Hybrid)</t>
+          <t>Software Engineerâ€“ Full Stack</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Azure ML, MLflow, Docker, Kubernetes, AKS, CI/CD</t>
+          <t>Generative AI, RAG, S3, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179f845817d9c394</t>
+          <t>https://www.indeed.com/viewjob?jk=845b1ae798305d08</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer (FDE)</t>
+          <t>SW Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery, PostgreSQL, MySQL</t>
+          <t>LangChain, RAG, Docker, Kubernetes, Jenkins, Git, Kafka, MySQL, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
+          <t>https://www.indeed.com/viewjob?jk=a9957a07b3110fb6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Solutions Architect | US</t>
+          <t>Automation Test Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cuesta Partners</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Hugging Face, TensorFlow, PyTorch, OpenCV, BigQuery, MLflow, Docker</t>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, CI/CD, Jenkins, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a29f61f02164cc</t>
+          <t>https://www.indeed.com/viewjob?jk=7f81cf0bf7eadd2e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>AI Engineer - Software</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Omitron Inc</t>
+          <t>General Dynamics Electric Boat</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Groton, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, MySQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec43ad9e8184093c</t>
+          <t>https://www.indeed.com/viewjob?jk=c810cf0067fe673b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Developer, Automation</t>
+          <t>Software Engineer III - Frontend, Monday.com, AWS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MySQL, Python</t>
+          <t>RAG, S3, CI/CD, Jenkins, Git, Databricks, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36278831392884e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21285074de6c55</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Full Stack Java Software Engineer III - React / AI / Kubernetes</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Data Lake, Git, Snowflake, Kafka, Tableau, Power BI, Python</t>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,54 +706,54 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbdf62f4fcd37bb</t>
+          <t>https://www.indeed.com/viewjob?jk=32e5a58b8c66532d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Solutions Architect (Remote)</t>
+          <t>Full Stack Java Software Engineer III - React / AI / Kubernetes</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23122d038602c127</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8ea7d11c89e330</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Solutions Architect (Remote)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>Elm Street Technology, LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+          <t>Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c550bf8810c96</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fa7dd1988be709</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Solutions Architect (Remote)</t>
+          <t>Aftermarket Business Data Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+          <t>Data Scientist, RAG, Copilot, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb19fdabfeceb391</t>
+          <t>https://www.indeed.com/viewjob?jk=bccf509a94e1c6b2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Gemini, S3, CI/CD, Terraform, Git, Hadoop, SQL, R, Java</t>
+          <t>RAG, Apache Airflow, CI/CD, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894c050699a8cfaa</t>
+          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AWS/EKS Platform Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=67fa702d507513f9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Operations (Databricks/AI)</t>
+          <t>Software Engineer II - Automation Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Data Lake, CI/CD, Git, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22eb530ec4c57c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=8927a399ffc916bd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>BI Developer/ Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>Diversified Gas &amp; Oil</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Cortex, Dataflow, Snowflake, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28f64ff4a82786b</t>
+          <t>https://www.indeed.com/viewjob?jk=13c74ea333d70bc4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Full Stack Engineer</t>
+          <t>Data Scientist (Insurance Product)-Senior Associate</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hr@brxio.com</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Git, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7cf07a83a749259</t>
+          <t>https://www.indeed.com/viewjob?jk=5950f47e85023b2b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Power BI Developer (Hybrid)</t>
+          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Git, Snowflake, Databricks, Power BI, SQL, R, Scala, Optimization</t>
+          <t>RAG, CI/CD, Git, PySpark, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d752c9fe0b8d8e6b</t>
+          <t>https://www.indeed.com/viewjob?jk=175150f6472dcabf</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cirque du Soleil</t>
+          <t>Panasonic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Git, Snowflake, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bfd1c9155d948dd</t>
+          <t>https://www.indeed.com/viewjob?jk=5e91c3d941f2fd60</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Pinecone, CI/CD, Python, R, Optimization</t>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a1e8850a1b63516</t>
+          <t>https://www.indeed.com/viewjob?jk=258482f8f1ae5b1c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Pinecone, CI/CD, Python, R, Optimization</t>
+          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Git, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,42 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7d163b37ed7c13</t>
+          <t>https://www.indeed.com/viewjob?jk=4761f59996832938</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Scientist - Conversational AI</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ford de México</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f3c70c544d475fa</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-24.xlsx
+++ b/daily_matches/job_matches_2026-07-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer (LLM &amp; GenAI)</t>
+          <t>Senior GCP Data Engineer for Patient Safety Measure Engine</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Flipped.ai</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, PyTorch, GCP Vertex AI, FastAPI</t>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c681313934b33c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d3f3d22744f5363</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineerâ€“ Full Stack</t>
+          <t>Software Engineer III-Databricks</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,147 +521,147 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
+          <t>RAG, TensorFlow, EC2, Kubernetes, CI/CD, Terraform, Databricks, PySpark, Kafka, Cassandra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845b1ae798305d08</t>
+          <t>https://www.indeed.com/viewjob?jk=4788de97836b6e30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SW Engineer - Sr. Consultant level</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Docker, Kubernetes, Jenkins, Git, Kafka, MySQL, NoSQL, SQL</t>
+          <t>RAG, Data Lake, CI/CD, Jenkins, Terraform, Git, Databricks, Kafka, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9957a07b3110fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Automation Test Engineer II</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Docker, CI/CD, Jenkins, Git, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f81cf0bf7eadd2e</t>
+          <t>https://www.indeed.com/viewjob?jk=4beac6cc3645a53b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer - Software</t>
+          <t>Fullstack Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>General Dynamics Electric Boat</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Groton, CT, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Python, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, CI/CD, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c810cf0067fe673b</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc0050b6863afe1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend, Monday.com, AWS</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Jenkins, Git, Databricks, Python, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Pinecone, CI/CD, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21285074de6c55</t>
+          <t>https://www.indeed.com/viewjob?jk=dd32d2a3e0a2f838</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Java Software Engineer III - React / AI / Kubernetes</t>
+          <t>Senior DevOps Engineer - Kubernetes &amp; Azure Cloud</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Kafka, R, Java, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e5a58b8c66532d</t>
+          <t>https://www.indeed.com/viewjob?jk=1e4f0a8212809077</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Java Software Engineer III - React / AI / Kubernetes</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Diversified Services Network</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Kafka, R, Java, Scala</t>
+          <t>Data Scientist, BigQuery, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,427 +741,42 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8ea7d11c89e330</t>
+          <t>https://www.indeed.com/viewjob?jk=db1faeb6819ff339</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Science Senior Associate- Card Data &amp; Analytics team</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Elm Street Technology, LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fa7dd1988be709</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Aftermarket Business Data Analyst</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>KLA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ann Arbor, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bccf509a94e1c6b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>First Citizens Bank</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Apache Airflow, CI/CD, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Comcast</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67fa702d507513f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8927a399ffc916bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>BI Developer/ Analyst</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Diversified Gas &amp; Oil</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Cortex, Dataflow, Snowflake, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13c74ea333d70bc4</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Data Scientist (Insurance Product)-Senior Associate</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5950f47e85023b2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, PySpark, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=175150f6472dcabf</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer II</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Panasonic</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e91c3d941f2fd60</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Full Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Intercontinental Exchange</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=258482f8f1ae5b1c</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Data Scientist Senior Associate</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Git, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4761f59996832938</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Data Scientist - Conversational AI</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Ford de México</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f3c70c544d475fa</t>
+          <t>https://www.indeed.com/viewjob?jk=7b365f4c5c760dbc</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-24.xlsx
+++ b/daily_matches/job_matches_2026-07-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer for Patient Safety Measure Engine</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Hugging Face, Pinecone, Prompt Engineering, PyTorch, S3, MLflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d3f3d22744f5363</t>
+          <t>https://www.indeed.com/viewjob?jk=b019316b66042eb5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III-Databricks</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, EC2, Kubernetes, CI/CD, Terraform, Databricks, PySpark, Kafka, Cassandra</t>
+          <t>Data Scientist, RAG, BigQuery, Data Lake, Dataflow, CI/CD, Terraform, BigQuery, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4788de97836b6e30</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Jenkins, Terraform, Git, Databricks, Kafka, R, Scala</t>
+          <t>S3, Terraform, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=e00458dd00ce6b98</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Full-Stack Engineer [Full Time; 100% remote; US-only]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hive Collective</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R, Java</t>
+          <t>RAG, Docker, Terraform, Git, PostgreSQL, MongoDB, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4beac6cc3645a53b</t>
+          <t>https://www.indeed.com/viewjob?jk=f19553ea058d111b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer</t>
+          <t>Senior Data Quality &amp; Active Learning AI Engineer (Plymouth)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Plymouth, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc0050b6863afe1</t>
+          <t>https://www.indeed.com/viewjob?jk=6954092e37693985</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Quality Assurance Architect (AI &amp; Automation Engineering)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Pinecone, CI/CD, Python, R, Optimization</t>
+          <t>Generative AI, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd32d2a3e0a2f838</t>
+          <t>https://www.indeed.com/viewjob?jk=5fbeba114947a5c4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Kubernetes &amp; Azure Cloud</t>
+          <t>AI / DevOps Engineer – Agentic Systems &amp; Automation</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,77 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e4f0a8212809077</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Diversified Services Network</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Peoria, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Scientist, BigQuery, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db1faeb6819ff339</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Data Science Senior Associate- Card Data &amp; Analytics team</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b365f4c5c760dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=d94a6f004e9ec281</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-24.xlsx
+++ b/daily_matches/job_matches_2026-07-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Hadoop Solutions Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Copilot, Hugging Face, Pinecone, Prompt Engineering, PyTorch, S3, MLflow</t>
+          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b019316b66042eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=5b43cb1da9bd5e66</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Data Lake, Dataflow, CI/CD, Terraform, BigQuery, Tableau, Power BI</t>
+          <t>RAG, S3, EC2, Glue, Redshift, Kinesis, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca7ef41ca26d3ec</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S3, Terraform, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, S3, EC2, Glue, Redshift, Kinesis, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00458dd00ce6b98</t>
+          <t>https://www.indeed.com/viewjob?jk=6bea0599e34ce74e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer [Full Time; 100% remote; US-only]</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hive Collective</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Terraform, Git, PostgreSQL, MongoDB, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Copilot, TensorFlow, PyTorch, S3, CI/CD, Jenkins, Git, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19553ea058d111b</t>
+          <t>https://www.indeed.com/viewjob?jk=39a86a30946c6486</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Quality &amp; Active Learning AI Engineer (Plymouth)</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plymouth, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Python, SQL, R, Scala</t>
+          <t>RAG, Synapse, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6954092e37693985</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24836d15aa901f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Quality Assurance Architect (AI &amp; Automation Engineering)</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Synapse, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,707 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fbeba114947a5c4</t>
+          <t>https://www.indeed.com/viewjob?jk=f56342ea02089099</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI / DevOps Engineer – Agentic Systems &amp; Automation</t>
+          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=024ce94c4237b353</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>OEConnection</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e08d2c63dac884c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Foundational ML, AI for Biology &amp; Translation (AIBT)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Genentech</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, PyTorch, S3, EC2, Kubernetes, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c08eb28be904a6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Foundational ML, AI for Biology &amp; Translation (AIBT)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Genentech</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, PyTorch, S3, EC2, Kubernetes, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2ecf86a2d8ec0c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Python Software Architect</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d70d40d60ab2d22</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>OCI Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e360996f49b9bba</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Java Application Architect</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=961ed4e278a33edd</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Enterprise ServiceNow Architect</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc18d561962fcd21</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20d65d994c35df77</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Great American Insurance Group</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Pinecone, Prompt Engineering, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54a3b318fd40bfd4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior .NET Solutions Developer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1548a514c44f0a9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Test Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f73b61f08926eb79</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Junior Data Engineer/Junior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>New York, NY, US USA</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Git, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8dfb5a97c30d3911</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Junior Data Engineer/Junior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Git, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e256a7935e4f4d48</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, S3, FastAPI, CI/CD, Terraform, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=861aca7e451d31b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Container Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d94a6f004e9ec281</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b12ac3bb4713b71</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Full Stack .NET Developer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Git, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b5188ac272515ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Software Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>vCluster Labs</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b86e991af2eecef</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Software Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>vCluster Labs</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe9cb9482e8e1df7</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-24.xlsx
+++ b/daily_matches/job_matches_2026-07-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hadoop Solutions Developer</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>RAG, S3, EC2, Glue, Athena, Data Lake, MLflow, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b43cb1da9bd5e66</t>
+          <t>https://www.indeed.com/viewjob?jk=530025f520e267c1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Senior Systems Engineer - Delivery DevOps</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Redshift, Kinesis, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>BigQuery, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, BigQuery, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca7ef41ca26d3ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Redshift, Kinesis, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>S3, EC2, Data Lake, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bea0599e34ce74e</t>
+          <t>https://www.indeed.com/viewjob?jk=76545a7a26014492</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Finastra</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, TensorFlow, PyTorch, S3, CI/CD, Jenkins, Git, NoSQL</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, FAISS, Pinecone, ChromaDB, Prompt Engineering, CI/CD, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a86a30946c6486</t>
+          <t>https://www.indeed.com/viewjob?jk=8986c8f990698680</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
+          <t>RAG, S3, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24836d15aa901f</t>
+          <t>https://www.indeed.com/viewjob?jk=6a9fb68922a90c5c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Forward Deploy Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f56342ea02089099</t>
+          <t>https://www.indeed.com/viewjob?jk=b7a21be93108e1cb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
+          <t>Senior Platform &amp; Integration Engineer (Kafka)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ce94c4237b353</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1e479ebfe2163b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
+          <t>Data Engineer / Data Analyst Associate - Business Transformation</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Embark, LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Synapse, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08d2c63dac884c6</t>
+          <t>https://www.indeed.com/viewjob?jk=ac63b78ecefaf2a0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Foundational ML, AI for Biology &amp; Translation (AIBT)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, PyTorch, S3, EC2, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>Data Scientist, RAG, Prompt Engineering, FastAPI, Docker, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c08eb28be904a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Foundational ML, AI for Biology &amp; Translation (AIBT)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Remofirst</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, PyTorch, S3, EC2, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>AI Engineer, RAG, S3, Glue, Athena, Redshift, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,102 +811,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ecf86a2d8ec0c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d17d64364a88e15a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Computer Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Integrated Solutions for Systems</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Aberdeen, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d70d40d60ab2d22</t>
+          <t>https://www.indeed.com/viewjob?jk=fc858ca9dbe3379f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Computer Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Integrated Solutions for Systems</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn, AL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e360996f49b9bba</t>
+          <t>https://www.indeed.com/viewjob?jk=59d41b3527005678</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Senior Agentic Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>arrivia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, SQL, R</t>
+          <t>Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961ed4e278a33edd</t>
+          <t>https://www.indeed.com/viewjob?jk=7d454c56d0e45130</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Enterprise ServiceNow Architect</t>
+          <t>Creative Product Technologist, Data &amp; AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wasserman Media Group LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc18d561962fcd21</t>
+          <t>https://www.indeed.com/viewjob?jk=29cc8f347a141c40</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Prompt Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+          <t>LangChain, RAG, LLaMA, Copilot, AKS, CI/CD, Git, R, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20d65d994c35df77</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa246d1d917fa83</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+          <t>CI/CD, Databricks, Kafka, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
+          <t>https://www.indeed.com/viewjob?jk=fcc108d020014d64</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>AI Engineer I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Great American Insurance Group</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Pinecone, Prompt Engineering, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54a3b318fd40bfd4</t>
+          <t>https://www.indeed.com/viewjob?jk=47b2c74a69a50c20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior .NET Solutions Developer</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1548a514c44f0a9d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d059dc898449f83</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Associate Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+          <t>S3, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73b61f08926eb79</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4ff182033422db</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Junior Data Engineer/Junior Data Scientist</t>
+          <t>Customer Engineer, Data &amp; Analytics Req#112</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Git, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, Git, BigQuery, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dfb5a97c30d3911</t>
+          <t>https://www.indeed.com/viewjob?jk=6eca18bb626b2a5b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Junior Data Engineer/Junior Data Scientist</t>
+          <t>Senior Engineer, QA Automation</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SoundExchange, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Git, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e256a7935e4f4d48</t>
+          <t>https://www.indeed.com/viewjob?jk=995eaa8eaffd3bcc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Infrastructure Solution Engineer- Sr Consultant I</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, S3, FastAPI, CI/CD, Terraform, NoSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861aca7e451d31b1</t>
+          <t>https://www.indeed.com/viewjob?jk=2207d35bba085e99</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Vision Square Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>Generative AI, Prompt Engineering, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,112 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12ac3bb4713b71</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Full Stack .NET Developer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Git, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b5188ac272515ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Senior Software Quality Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>vCluster Labs</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b86e991af2eecef</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior Software Quality Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>vCluster Labs</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9cb9482e8e1df7</t>
+          <t>https://www.indeed.com/viewjob?jk=cfdbf4cc7bbe8019</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-24.xlsx
+++ b/daily_matches/job_matches_2026-07-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Athena, Data Lake, MLflow, FastAPI, Docker, CI/CD</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530025f520e267c1</t>
+          <t>https://www.indeed.com/viewjob?jk=935ece4128fe6f9f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Delivery DevOps</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>PURE Insurance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BigQuery, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, BigQuery, PostgreSQL, MySQL</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Copilot, Prompt Engineering, PyTorch, FastAPI, Docker, AKS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
+          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>J&amp;B Medical</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Wixom, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S3, EC2, Data Lake, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>S3, EC2, Athena, Redshift, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76545a7a26014492</t>
+          <t>https://www.indeed.com/viewjob?jk=41ea01c619cf5f4e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Finastra</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, FAISS, Pinecone, ChromaDB, Prompt Engineering, CI/CD, Git</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8986c8f990698680</t>
+          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Engineer, Python &amp; API Development</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>Webcreek</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a9fb68922a90c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=3914b85835c19c86</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Forward Deploy Engineer</t>
+          <t>Sr. Java Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python</t>
+          <t>Generative AI, RAG, Copilot, Jenkins, Git, Kafka, PostgreSQL, MongoDB, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7a21be93108e1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=d3327e077854ee22</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; Integration Engineer (Kafka)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
+          <t>Generative AI, RAG, Synapse, CI/CD, Git, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1e479ebfe2163b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer / Data Analyst Associate - Business Transformation</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Embark, LLC</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Synapse, CI/CD, Git, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac63b78ecefaf2a0</t>
+          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, FastAPI, Docker, Git, Databricks, Python, SQL, R</t>
+          <t>Generative AI, RAG, Synapse, CI/CD, Git, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
         </is>
       </c>
     </row>
@@ -788,20 +788,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Remofirst</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, S3, Glue, Athena, Redshift, Redshift, Python, SQL, R</t>
+          <t>Generative AI, RAG, Synapse, CI/CD, Git, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17d64364a88e15a</t>
+          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Computer Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Integrated Solutions for Systems</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aberdeen, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
+          <t>Generative AI, RAG, Synapse, CI/CD, Git, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc858ca9dbe3379f</t>
+          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Computer Scientist</t>
+          <t>Development Operations Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Integrated Solutions for Systems</t>
+          <t>University of Alabama</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Auburn, AL, US USA</t>
+          <t>Tuscaloosa, AL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
+          <t>RAG, BigQuery, Docker, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d41b3527005678</t>
+          <t>https://www.indeed.com/viewjob?jk=74b2fdb0c7bef0a3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Agentic Software Engineer</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>arrivia</t>
+          <t>Empower Pharmacy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d454c56d0e45130</t>
+          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Creative Product Technologist, Data &amp; AI</t>
+          <t>Development Operations Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wasserman Media Group LLC</t>
+          <t>University of Alabama</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Tuscaloosa, AL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>RAG, BigQuery, Docker, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29cc8f347a141c40</t>
+          <t>https://www.indeed.com/viewjob?jk=eb1c44e7469936c5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Prompt Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, AKS, CI/CD, Git, R, Scala, A/B Testing</t>
+          <t>LangChain, RAG, LLaMA, Hugging Face, S3, Docker, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa246d1d917fa83</t>
+          <t>https://www.indeed.com/viewjob?jk=7819032a905b39d1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Portfolio Management Group Tech AI Engineer, Associate</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CI/CD, Databricks, Kafka, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcc108d020014d64</t>
+          <t>https://www.indeed.com/viewjob?jk=594bd78fc65fc18b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Engineer I</t>
+          <t>Senior Applied ML Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Middleton, WI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Snowflake, Python, SQL, R</t>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, MLflow, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47b2c74a69a50c20</t>
+          <t>https://www.indeed.com/viewjob?jk=c544015c37d115ac</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>Senior Security Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, MongoDB, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d059dc898449f83</t>
+          <t>https://www.indeed.com/viewjob?jk=6dea8652a5b795a3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Associate Cloud &amp; DevOps Engineer</t>
+          <t>Senior Security Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>S3, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Git, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, MongoDB, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4ff182033422db</t>
+          <t>https://www.indeed.com/viewjob?jk=4ad0bea127343113</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Customer Engineer, Data &amp; Analytics Req#112</t>
+          <t>Senior Security Engineer II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, Dataflow, Git, BigQuery, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, MongoDB, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eca18bb626b2a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=30c0374164221a52</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Engineer, QA Automation</t>
+          <t>Senior Security Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SoundExchange, Inc.</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, MongoDB, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995eaa8eaffd3bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=ece3940d49ed0e83</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Infrastructure Solution Engineer- Sr Consultant I</t>
+          <t>E T Consultant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Gemini, Copilot, EC2, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,42 +1231,322 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2207d35bba085e99</t>
+          <t>https://www.indeed.com/viewjob?jk=03c0959a1cd76de4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Test Tooling Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vision Square Inc</t>
+          <t>Tiger Data</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2da8bdcc1ae85a89</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Software Engineer – Agentic AI</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Thombara, LLC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>10</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Generative AI, Prompt Engineering, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cfdbf4cc7bbe8019</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4443b2357ab0fb43</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LPL Financial</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=acfa3c8de5699bc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Chorus</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ZoomInfo</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Kafka, NoSQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39316c6a60f94d00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer (Azure)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5665b0a9ef664955</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AWS Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cloud and Things</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3a616293a442292</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NIKE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Beaverton, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Glue, Docker, Git, Databricks, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74bc20590c525b7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Completions &amp; Well Management Research Engineer - Advanced</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Databricks, Power BI, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e64a451341fb3b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Technical Support Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Metrc</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=541c513c1c0789cc</t>
         </is>
       </c>
     </row>
